--- a/resultado/resultados_com_telefone.xlsx
+++ b/resultado/resultados_com_telefone.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H117"/>
+  <dimension ref="A1:H239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4662,6 +4662,4422 @@
         </is>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>RUA BENGALI, 131</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>PARQUE NOVO ORATÓRIO I</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>SANTO ANDRE</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Residencial (A - 2)</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>1059116</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(11) 96907-4414</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>AVENIDA MARECHAL TITO, 3517</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>VILA CURUCA</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Comercial (C - 2)</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>1059117</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(11) 2025-5125 / (11) 2571-1646 / 11 4066 7911</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>RUA CANANÉIA, 157</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>DIADEMA</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Serviço profissional (D - 1)</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>1059118</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(11) 4043-0978</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>RUA ALVINO GOMES TEIXEIRA, 2140</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>JARDIM GUANABARA</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>PRESIDENTE PRUDENTE</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>1059119</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(18) 99803-5234 / (18) 99721-5369</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>RUA LUIZA FAVARO, 40</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>JARDIM ITACOLOMI</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Local de reunião de Público (F - 8)</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>1059120</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(11) 98870-2139</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>RUA NATALINO FABRINI, 43</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>VILA NOGUEIRA</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>DIADEMA</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>1059121</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(47) 3301-6100 / (11) 99222-4129</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>RUA LUÍS PINTO FLÁQUER, 113</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>SANTO ANDRE</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Serviço profissional (D - 1)</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>1059122</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(11) 96813-7939 / (11) 4994-6766</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>RODOVIA SP 305, 280</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>DISTRITO INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>MONTE ALTO</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>1059123</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(16) 3244-3100 / 16 3241-1009 / 16 3241-1640</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>AVENIDA CECÍLIA MEIRELES, nº 265 e 269 COM A RUA GUSTAVO TEIXEIRA, nº 12, 265</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>JARDIM NOSSA SENHORA APARECIDA</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AMERICANA</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Comercial (C - 2)</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>1059124</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(19) 98940-9998 / (19) 3469-2214 / (19) 3468.3962</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>TRAVESSA PLANEJADA, 7</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>TABOAO</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>GUARULHOS</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Serviço de saúde e institucional (H - 6)</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>1059125</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(11) 5468-6942 / (47) 3301-6100</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>RUA RODESIA, 450</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>PARQUE ORATÓRIO</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>SANTO ANDRE</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Local de reunião de Público (F - 8)</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>1059126</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(11) 95846-9395 / (11) 4476-5127 / 11 4476-5127</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>AVENIDA BRASIL, 497</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>CEDRAL</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>1059127</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(17) 3266 2291</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>RUA MARIA GODOY CANHOLI, 421</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>RESIDENCIAL MARÉ MANSA</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>PRESIDENTE PRUDENTE</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Serviço profissional (D - 1)</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>1059128</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(18)3907-4787</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>RUA ESTADOS UNIDOS, 1881</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>JARDIM AMERICA</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Serviço de saúde e institucional (H - 6)</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>1059129</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(11) 3058-2020 / (11) 4004-7821</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>AVENIDA PAULISTA, 12</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NOSSA SENHORA DE FATIMA</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AMERICANA</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Serviço profissional (D - 1)</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>1059130</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(19) 3648-0696 / (19) 3648-0714 / (19) 99941-5209</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>RUA BARÃO DO RIO BRANCO, 1855</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>ANDRADINA</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Serviço profissional (D - 1)</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>1059131</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(18) 3722-9090 / (18) 3702-1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>RAMALHO FRANCO, 141</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>PENAPOLIS</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>1059132</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(44) 99870-7686 / (18) 3653-6402 / (18) 3652-4568</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>RUA JORGE BERETA, 571</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>PARQUE ORATÓRIO</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>SANTO ANDRE</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Comercial (C - 2)</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>1059133</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>11 97313-6195 / 11 94025-0285 / (11) 4479-8888</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>AVDENIDA ARTHUR COSTA FILHO, 34</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>CARAGUATATUBA</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Local de reunião de Público (F - 8)</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>1059134</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(12) 3883-4407 / (12) 99710-9900</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>RUA SARJOB MENDES, 350</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>JARDIM ICARAY</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>ARACATUBA</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>1059135</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(18) 99740-3344 / (18) 98103-7068 / (18) 99622-2724</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>AVENIDA PEDRO BUENO, 1396</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>CAMPO BELO</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Serviço automotivo e assemelhados (G - 4)</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>1059136</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(11) 2606-1011 / (11) 2606-4560 / (27)3711-8748</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>AV LUIZ MARTINS FILHO, 178</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>FAZENDA RIO PRETO - DISTRITO DE ENGENHEIRO SCHIMDT</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>SAO JOSE DO RIO PRETO</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Comercial (C - 2)</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>1059137</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>TELEFONE NÃO EXISTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>RODOVIA SP 563, 0</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>RURAL</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>ANDRADINA</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Serviço profissional (D - 1)</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>1059138</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(18) 98138-3997 / (18)98120-2600 / (18)98121-0693</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>AVENIDA SENADOR ROBERTO SÍMONSEN, 785</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>SAO CAETANO DO SUL</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>1059139</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>11 4020-2208 / (11) 4220-5211</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>RUA SEBASTIÂO SAMPAIO, 2461</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>JARDIM SÃO SEBASTIÃO</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>SERTAOZINHO</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Serviço profissional (D - 1)</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>1059140</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(16) 3945-8468 / (16) 98216-0368</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>RUA CRISTIANO OLSEN, 1930</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Higienópolis</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>ARACATUBA</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Educacional e cultura física (E - 4)</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>1059141</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>18 98175-7095</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>AVENIDA SENADOR ROBERTO SÍMONSEN, 643</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>SAO CAETANO DO SUL</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Comercial (C - 2)</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>1059142</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(11) 2311-2846 / (11) 98571-9600</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>RUA ALVARENGA PEIXOTO, 328</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>JARDIM BRASILANDIA</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>SOROCABA</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>1059143</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(11) 98922-1142</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>RODOVIA PROFESSOR ZEFERINO VAZ, 0</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>CENTRO (TUJUGUABA)</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>CONCHAL</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Indústria (I - 1)</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>1059144</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(19) 3866-2312 / (19) 3866-8600</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>RUA CHICO ALVES, 212</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>ENSEADA</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>UBATUBA</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Indústria (I - 2)</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>1059145</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>TELEFONE NÃO EXISTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>AVENIDA NORMA VALÉRIO CORRÊA, 556</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>JD BOTANICO</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>RIBEIRAO PRETO</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>1059146</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>11 4020-2208</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>AVENIDA COMENDADOR MANÇOR DAUD, 621</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>JARDIM SANTA LUZIA</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>SAO JOSE DO RIO PRETO</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Serviço profissional (D - 1)</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>1059147</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>(17) 3353-3001</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>RUA BANIBAS, 294</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>ALTO DE PINHEIROS</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Educacional e cultura física (E - 3)</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>1059148</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>(11) 91222-8205 / (11) 91222-8185</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>RUA APARECIDA DO TABOADO, 2233</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Eldorado</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>SAO JOSE DO RIO PRETO</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>1059149</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(17)99652-0317 / (17) 98231-0139</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>RUA SENADOR VERGUEIRO, 1240</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>LIMEIRA</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Educacional e cultura física (E - 2)</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>1059150</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(19) 3495-5838 / (19) 99909-4217</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>AVENIDA DOUTOR JOÃO PALMA GUIÃO, 1210</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>ALTO DA BOA VISTA</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>RIBEIRAO PRETO</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>1059151</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>(16) 99355-7977 / (21) 99612-0251</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>AVENIDA PAPA JOÃO PAULO II, 543</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>JARDIM PLANALTO</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>CONCHAL</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>1059152</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>(19) 3866-3948</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>RUA MINAS GERAIS, 2878</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>PATRIMONIO NOVO</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>VOTUPORANGA</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Serviço profissional (D - 1)</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>1059153</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(17) 3421-2374 / (17) 99773-6636</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>AVENIDA DOUTOR WILSOM DE SOUZA FOZ, 4376</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NOVA BOA VISTA</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>VOTUPORANGA</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>1059154</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>(14) 3679-7800 / (14) 99605-0398</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>RUA VISCONDE DE RIO BRANCO, 196</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>SAO JOAO DA BOA VISTA</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Comercial (C - 2)</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>1059155</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(19) 99582-4320 / (19) 3633-4320 / (19) 3623-2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>RUA FLORIANO PEIXOTO, 517</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>ARACATUBA</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Serviço de saúde e institucional (H - 6)</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>1059156</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(18) 3623-2553 / (18) 3625-5394 / (18) 3519-1428</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>RUA PREFEITO JUSTINO PAIXÃO, 248</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>SANTO ANDRE</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Educacional e cultura física (E - 1)</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>1059157</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>(11) 2325-6500 / (11) 4996-1437 / (11) 93946-6440</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>AV LUIZ DUMONT VILLARES,, 1565</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>PARADA INGLESA</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Serviço profissional (D - 1)</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>1059158</v>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>(11) 97183-0999</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>AVENIDA FRANCISCO MONTEIRO, 2379</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>BOSQUE SANTANA</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>RIBEIRAO PIRES</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>1059159</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>(11) 94322-6834 / (11) 2533-6613 / (11) 5591-7077</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>JOSE GREGORINI, 306</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>CORINTO</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>FERNANDOPOLIS</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>1059160</v>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>(17) 3465-6250 / (17) 98814-0373</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>AVENIDA GUAPIRA, 2497</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>TUCURUVI</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Local de reunião de Público (F - 8)</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>1059161</v>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>(11) 5698-8000</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>RUA RIO BRANCO, 456</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>CASTILHO</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Serviço de saúde e institucional (H - 6)</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>1059162</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>21 3278-9222</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>RUA FRANCISCO ROMEIRO SOBRINHO, 20</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>SANTO AMARO</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Comercial (C - 2)</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>1059163</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>(11) 98733-5208</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>AVENIDA EMÍLIO RIBAS, 2597</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>VILA GALVÃO</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>GUARULHOS</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Serviço profissional (D - 1)</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>1059164</v>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>(11) 4307-9795 / (11) 2452-3364</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>RUA PAULO PORTMAN, 9</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>ARRAIAL PAULISTA</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>TABOAO DA SERRA</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Comercial (C - 2)</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>1059165</v>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>(11) 4135-8804 / (15) 3211-2631</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>AVENIDA BARÃO DE MAUA, 3765</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>SÃO JOÃO</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>MAUA</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Serviço profissional (D - 3)</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>1059166</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>(11) 91499-3510 / (11)4512-7758</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>1059167</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>SEM ENDEREÇO</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>RUA DOUTOR ARMANDO SALES DE OLIVEIRA, 385</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>LEME</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>1059168</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>(19) 3097-1000 / (19) 2666-0957 / (19) 2385-0099</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>RUA PRINCESA ISABEL, 241</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>ARACATUBA</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>1059169</v>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>18 99745-5769</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>RUA WALTER SEDLACEK, 395</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>CHACARAS ARCO IRIS</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>ARACATUBA</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Indústria (I - 2)</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>1059170</v>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>(18) 99652-2095</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>AVENIDA NAVARRO DE ANDRADE, 1161</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>SANTA FE DO SUL</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G173" t="n">
+        <v>1059171</v>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>(17) 3631-3322 / (17) 3641-2051 / (17) 3641-9160</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>RUA DOUTOR ROMEU FURLANETO, 274</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>SAO JOAO DA BOA VISTA</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Serviço profissional (D - 1)</t>
+        </is>
+      </c>
+      <c r="G174" t="n">
+        <v>1059172</v>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>(19) 3631.4433 / (19) 3633.8504</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr"/>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>RUA JULIETA MACEDO PEREIRA, 176</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>RIBEIRÂNIA</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>RIBEIRAO PRETO</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Serviço profissional (D - 1)</t>
+        </is>
+      </c>
+      <c r="G175" t="n">
+        <v>1059173</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>TELEFONE NÃO EXISTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr"/>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>RUA ÁURELIANO GARCÍA DE OLIVEIRA, 229</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>NOVA RIBEIRÂNIA</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>RIBEIRAO PRETO</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G176" t="n">
+        <v>1059174</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>(16) 99233-7272 / 16 99779-9710 / (16) 3916-4045</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr"/>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>PRAÇA SERRA DO OROCORI, 38</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>ITAIM PAULISTA</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G177" t="n">
+        <v>1059175</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>(11) 2743-3437 / (11) 3279-8800</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr"/>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>AVENIDA MARECHAL TITO, 2498</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>SAO MIGUEL</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Serviço profissional (D - 1)</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>1059176</v>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>(11) 2956-2333 / (11) 2956-5876 / (11) 2025-2845</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr"/>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>RUA SIDNEI, 210</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>VILA METALÚRGICA</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>SANTO ANDRE</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Serviço profissional (D - 1)</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
+        <v>1059177</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>(11) 3429-5894</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>MARIA PERECINEI MONACO, 981</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>JARDIM DAS ROSAS ll</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>JABOTICABAL</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Indústria (I - 2)</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
+        <v>1059178</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>(16) 3202-0002</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G181" t="n">
+        <v>1059179</v>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>SEM ENDEREÇO</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>RUA ANA LUIZA, 162</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>CASTELO</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>BATATAIS</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Comercial (C - 2)</t>
+        </is>
+      </c>
+      <c r="G182" t="n">
+        <v>1059180</v>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>(16) 99198-8679 / (16) 2110-0496 / (16)2110-0496</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>RUA BRIGADEIRO TOBIAS, 77</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>REGENTE FEIJO</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G183" t="n">
+        <v>1059181</v>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>(18) 99671-8531 / (18) 3279-1455 / (18) 3279-1034</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>RUA COSTA AGUIAR, 1861</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>IPIRANGA</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Serviço de saúde e institucional (H - 6)</t>
+        </is>
+      </c>
+      <c r="G184" t="n">
+        <v>1059182</v>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>(11) 2574-6500</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G185" t="n">
+        <v>1059183</v>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>SEM ENDEREÇO</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr"/>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>RUA JOSÉ ANTONIO CAPEL SANCHES, 632</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Residencial Portal da Perola II</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>BIRIGUI</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Indústria (I - 1)</t>
+        </is>
+      </c>
+      <c r="G186" t="n">
+        <v>1059184</v>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>(18) 99602-5143 / (18) 98125-7623</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>AVENIDA JOAO CARLOS DA SILVA BORGES, 764</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>SANTO AMARO</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Local de reunião de Público (F - 8)</t>
+        </is>
+      </c>
+      <c r="G187" t="n">
+        <v>1059185</v>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>(11) 97532-4548 / (11) 4328-6205 / 11 4328-6205</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>AVENIDA NOSSA SENHORA DO SABARA, 1946</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>CAMPO GRANDE</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Serviço automotivo e assemelhados (G - 3)</t>
+        </is>
+      </c>
+      <c r="G188" t="n">
+        <v>1059186</v>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>(11) 5521-3070 / (11) 95931-9807 / (11) 5631-3872</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>RUA VICENTE GOLFETO, 179</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>CAMPOS ELISEOS</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>RIBEIRAO PRETO</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Comercial (C - 2)</t>
+        </is>
+      </c>
+      <c r="G189" t="n">
+        <v>1059187</v>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>(16) 3626-4005</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr"/>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>RUA RUI BARBOSA, 5</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>JD PAULO LUPINO</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>TORRINHA</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Educacional e cultura física (E - 1)</t>
+        </is>
+      </c>
+      <c r="G190" t="n">
+        <v>1059188</v>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>(14)3656-1197</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr"/>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>RUA BENEDITO MARIANO LEITE, 598</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>BARRA VELHA</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>ILHABELA</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Serviço profissional (D - 1)</t>
+        </is>
+      </c>
+      <c r="G191" t="n">
+        <v>1059189</v>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>(12) 99237-4622 / 12 99237-4622 / 12 99210-2773</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr"/>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>AVENIDA SENADOR CÉSAR VERGUEIRO, 1017</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>JD IRAJÁ</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>RIBEIRAO PRETO</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G192" t="n">
+        <v>1059190</v>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>(16) 3916-3333 / (16) 3600-8700 / (16) 3234-0248</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr"/>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>AV PAES DE BARROS, 2824</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>PARQUE DA MOOCA</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Serviço de saúde e institucional (H - 1)</t>
+        </is>
+      </c>
+      <c r="G193" t="n">
+        <v>1059191</v>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>(11) 2274-3632 / (11) 2274 3632</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr"/>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>RUA MARIA MARCOLINA, 289</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>BRAS</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G194" t="n">
+        <v>1059192</v>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>(11) 95052-2764 / (11) 2694-7102</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr"/>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>RUA SALVADOR COSSO, 233</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>JD IRAJÁ</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>RIBEIRAO PRETO</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Comercial (C - 2)</t>
+        </is>
+      </c>
+      <c r="G195" t="n">
+        <v>1059193</v>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>(16) 99172-5262 / 11 4020-2208</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr"/>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>AVENIDA PEDRO VITAL, 520</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>JARDIM SANTANA</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>MONTE ALTO</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Serviço profissional (D - 1)</t>
+        </is>
+      </c>
+      <c r="G196" t="n">
+        <v>1059194</v>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>(16) 99748-3269 / (16) 98216-1508</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr"/>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>RUA DO CARLÃO, 370</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>VILA LUCINDA</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>SANTO ANDRE</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Serviço automotivo e assemelhados (G - 2)</t>
+        </is>
+      </c>
+      <c r="G197" t="n">
+        <v>1059195</v>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>(11) 4435-1370</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr"/>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>RUA MARCILIO DIAS, 184</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>ALVARES MACHADO</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Serviço automotivo e assemelhados (G - 3)</t>
+        </is>
+      </c>
+      <c r="G198" t="n">
+        <v>1059196</v>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>(18) 99719-0840 / (18) 3273-2391 / (18) 3273-1915</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr"/>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>AVENIDA VIVALDI, 1004</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>RUDGE RAMOS</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>SAO BERNARDO DO CAMPO</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Serviço profissional (D - 3)</t>
+        </is>
+      </c>
+      <c r="G199" t="n">
+        <v>1059197</v>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>(11) 94062-1310 / (11) 99810-8499 / (11) 97389 9999</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr"/>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>AVENIDA ALFREDO MALUF, 827</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>JARDIM SANTO ANTÔNIO</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>SANTO ANDRE</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Local de reunião de Público (F - 2)</t>
+        </is>
+      </c>
+      <c r="G200" t="n">
+        <v>1059198</v>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>(11) 5834-8430 / (11) 97676-6982 / (11)97676-6982</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>RUA MEDITERRÂNEO, 444</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>SAO BERNARDO DO CAMPO</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G201" t="n">
+        <v>1059199</v>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>(11) 98237-0539 / (11) 4332-9594 / 11 4332-7616</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>RUA BOM PASTOR, 1131</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>IPIRANGA</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Indústria (I - 1)</t>
+        </is>
+      </c>
+      <c r="G202" t="n">
+        <v>1059200</v>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>(11) 91900-7764 / (11) 99970-0687 / (11) 2050-9997</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>RUA DONÁ PRIMITIVA VIANCO, 605</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>OSASCO</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Serviço profissional (D - 1)</t>
+        </is>
+      </c>
+      <c r="G203" t="n">
+        <v>1059201</v>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>(11) 3681-9400 / (11) 97082-1815</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>R. CAP. SEBASTIAO ANTONIO DE CARVALHO, 20</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>JARDIM PAULISTA</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>CASA BRANCA</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Comercial (C - 2)</t>
+        </is>
+      </c>
+      <c r="G204" t="n">
+        <v>1059202</v>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>(19) 3671-1081 / (19) 98960-3545 / (19) 3671-6142</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>AV. DOUTOR SERGIO MACHADO BRAUNER, 435</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>TERRA PRETA</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>MAIRIPORA</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Comercial (C - 2)</t>
+        </is>
+      </c>
+      <c r="G205" t="n">
+        <v>1059203</v>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>(11) 4486-1427 / (11) 97561-8587 / 11 97561-8587</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>TRAVESSA JOAQUIM DA SILVA, 560</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>JARDIM SAIRA</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>SOROCABA</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Serviço profissional (D - 1)</t>
+        </is>
+      </c>
+      <c r="G206" t="n">
+        <v>1059204</v>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>TELEFONE NÃO EXISTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>PRAÇA BENEDITO CALIXTO, 121</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>JARDIM PAULISTA</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Comercial (C - 2)</t>
+        </is>
+      </c>
+      <c r="G207" t="n">
+        <v>1059205</v>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>(11) 3088-6311</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr"/>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>AVENIDA DOS EXPEDICIONÁRIOS, 120</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>FAZENDA BELÉM</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>FRANCO DA ROCHA</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Comercial (C - 2)</t>
+        </is>
+      </c>
+      <c r="G208" t="n">
+        <v>1059206</v>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>(11) 98966-8069 / (11) 4267-0020</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G209" t="n">
+        <v>1059207</v>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>SEM ENDEREÇO</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr"/>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>RUA BAHIA, 6</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>JD PLANALTO</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>ARUJA</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Serviço automotivo e assemelhados (G - 2)</t>
+        </is>
+      </c>
+      <c r="G210" t="n">
+        <v>1059208</v>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>11 2756-1500 / 11 2756-1510</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr"/>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>RUA TREZE DE MAIO, 340</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>VILA GALVÃO</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>GUARULHOS</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Serviço profissional (D - 1)</t>
+        </is>
+      </c>
+      <c r="G211" t="n">
+        <v>1059209</v>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>(11) 91346-2378 / (11) 2457-7000</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr"/>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>ACESSO AVENIDA ENGENHEIRO ANTÔNIO FRANCISCO DE PAULA S*, 2728</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>VILA GEORGIA</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>CAMPINAS</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Serviço automotivo e assemelhados (G - 4)</t>
+        </is>
+      </c>
+      <c r="G212" t="n">
+        <v>1059210</v>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>(19) 98148-3893</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr"/>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>AVENIDA GOVERNADOR JÂNIO QUADROS, 1101</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>PARQUE SÃO FRANCISCO</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>FERRAZ DE VASCONCELOS</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Local de reunião de Público (F - 8)</t>
+        </is>
+      </c>
+      <c r="G213" t="n">
+        <v>1059211</v>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>(11) 4677-9401 / (11) 98271-8307 / (11) 4678-5297</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr"/>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>RUA UBATÃ, 1180</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>JD SÃO DANIEL</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>CARAPICUIBA</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G214" t="n">
+        <v>1059212</v>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>TELEFONE NÃO EXISTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr"/>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>AVENIDA DA AMIZADE, 2983</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>SANTA ROSA II</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>SANTA BARBARA D OESTE</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G215" t="n">
+        <v>1059213</v>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>(19) 3473-0755</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr"/>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>AVENIDA ORLÂNDIA, 644</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>JARDIM SAO FRANCISCO</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>PIRACICABA</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Local de reunião de Público (F - 8)</t>
+        </is>
+      </c>
+      <c r="G216" t="n">
+        <v>1059214</v>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>(19)3424-4817 / (19)99625-1115</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr"/>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>ESTRADA FERNANDO NOBRE, 1299</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>PORTAL DA ROSOLANDIA</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>COTIA</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Local de reunião de Público (F - 8)</t>
+        </is>
+      </c>
+      <c r="G217" t="n">
+        <v>1059215</v>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>(11) 97283-3425</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr"/>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>AVENIDA GOV PEDRO DE TOLÊDO, 2674</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>BONFIM</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>CAMPINAS</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G218" t="n">
+        <v>1059216</v>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>(19) 3242-3871 / (19) 97126-8489 / (19) 3234-8646</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr"/>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>AVENIDA DOS REMÉDIOS, 1629</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>REMEDIOS</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>OSASCO</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Serviço automotivo e assemelhados (G - 4)</t>
+        </is>
+      </c>
+      <c r="G219" t="n">
+        <v>1059217</v>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>(21) 98390-8414 / (11) 95870-2779 / (11) 3602-5441</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr"/>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>AVENIDA LINS DE VASCONCELOS, 1018</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>CAMBUCI</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Local de reunião de Público (F - 8)</t>
+        </is>
+      </c>
+      <c r="G220" t="n">
+        <v>1059218</v>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>(11) 3542-5000 / (11) 3271-8622 / (11) 97398-9542</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G221" t="n">
+        <v>1059219</v>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>SEM ENDEREÇO</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr"/>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>AVENIDA JUCELINO KUBITSCHECK DE OLIVEIRA, 137</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>AGUARDENTE DO REINO</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>MOGI-MIRIM</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Serviço automotivo e assemelhados (G - 4)</t>
+        </is>
+      </c>
+      <c r="G222" t="n">
+        <v>1059220</v>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>TELEFONE NÃO EXISTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr"/>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>RUA JOSE PAOLONE, 78</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>SANTA PAULA</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>SAO CAETANO DO SUL</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G223" t="n">
+        <v>1059221</v>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>(11) 2311-2949 / (11) 3565-1880 / (11) 4225-1723</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr"/>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>RUA ROMEU CASTELUCCI, 250</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Parque Residencial São Marcos</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>PORTO FELIZ</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G224" t="n">
+        <v>1059222</v>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>(15) 98816-4789 / (15) 3261-7102</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr"/>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>AVENIDA BARÃO DE VALENÇA, 960</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>VILA REZENDE</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>PIRACICABA</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Comercial (C - 2)</t>
+        </is>
+      </c>
+      <c r="G225" t="n">
+        <v>1059223</v>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>(19) 3403-2800</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr"/>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>RUA GERACINA, 438</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>VILA JACUI</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Serviço profissional (D - 1)</t>
+        </is>
+      </c>
+      <c r="G226" t="n">
+        <v>1059224</v>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>(11) 2943-2861 / (11) 2026-4971</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr"/>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>VALE D'AOSTA 195, 195</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>JOÃO JABOUR</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>SALTO</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Serviço profissional (D - 4)</t>
+        </is>
+      </c>
+      <c r="G227" t="n">
+        <v>1059225</v>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>(41) 3097-4600 / (11) 4602-6370 / (11) 4029-2377</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr"/>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>RUA QUINZE DE NOVEMBRO, 75</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>JARDIM SANDRA MARIA</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>IBIUNA</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G228" t="n">
+        <v>1059226</v>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>(15) 3248-9880</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr"/>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>AVENIDA SANTOS DUMONT, 2075</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>CUMBICA</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>GUARULHOS</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Serviço profissional (D - 1)</t>
+        </is>
+      </c>
+      <c r="G229" t="n">
+        <v>1059227</v>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>(11) 2483-2000</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr"/>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>ACESSO AVENIDA DOS IMIGRANTES, 712</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>SANTA MONICA</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>SAO PEDRO</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Serviço automotivo e assemelhados (G - 4)</t>
+        </is>
+      </c>
+      <c r="G230" t="n">
+        <v>1059228</v>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>(19) 99969-7381 / (19) 3481-1039 / (19) 3483-1863</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr"/>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>AVENIDA JOAQUIM CONSTANTINO, 3980</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>JARDIM SÃO LUIS</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>PRESIDENTE PRUDENTE</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G231" t="n">
+        <v>1059229</v>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>(18) 3222-1428 / (18)3901-1891 / (18) 99818-3930</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr"/>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>RUA AMÉLIA EUGÊNIA, 472</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>DIADEMA</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Serviço profissional (D - 1)</t>
+        </is>
+      </c>
+      <c r="G232" t="n">
+        <v>1059230</v>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>(11) 5455-2789</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr"/>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>RUA SÃO PAULO, 4149</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>PATRIMÔNIO VELHO</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>VOTUPORANGA</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Comercial (C - 1)</t>
+        </is>
+      </c>
+      <c r="G233" t="n">
+        <v>1059231</v>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>(17) 3422-3001</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G234" t="n">
+        <v>1059232</v>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>SEM ENDEREÇO</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr"/>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>RUA FERNANDO PRESTES, 367</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>VILA BOA ESPERANÇA - 1ª SECCAO</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>OURINHOS</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Local de reunião de Público (F - 2)</t>
+        </is>
+      </c>
+      <c r="G235" t="n">
+        <v>1059233</v>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>(14) 3322-2506 / (11)3503-1250</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr"/>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>RUA ERNESTO CHIARINI DE UGO, 236</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>VILA ESPERANÇA</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>SANTO ANTONIO DE POSSE</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Serviço automotivo e assemelhados (G - 4)</t>
+        </is>
+      </c>
+      <c r="G236" t="n">
+        <v>1059234</v>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>TELEFONE NÃO EXISTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr"/>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>RUA DOS CRISÂNTEMOS, 30</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>SANTA MARTA</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>ITAPIRA</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Serviço de saúde e institucional (H - 6)</t>
+        </is>
+      </c>
+      <c r="G237" t="n">
+        <v>1059235</v>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>(21) 97168-0280 / (19) 2149-3045 / (19) 3813-1320</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr"/>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>RUA MERCEDES LOPES, 419</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>PENHA</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Comercial (C - 2)</t>
+        </is>
+      </c>
+      <c r="G238" t="n">
+        <v>1059236</v>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>(11) 2621-7735 / (11) 96716-2717</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>CLCB Vigente</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr"/>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>RUA JOSÉ ANTUNES, 361</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>TORRINHA</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Serviço profissional (D - 1)</t>
+        </is>
+      </c>
+      <c r="G239" t="n">
+        <v>1059237</v>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>(14) 3656-1916 / (14) 3767 1133 / (14) 3656-9600</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
